--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <si>
     <t>Origin</t>
   </si>
@@ -26,6 +26,42 @@
     <t>Multiple</t>
   </si>
   <si>
+    <t>Abbottabad</t>
+  </si>
+  <si>
+    <t>Abdul Hakim</t>
+  </si>
+  <si>
+    <t>Ahmed Pur East</t>
+  </si>
+  <si>
+    <t>Alipur</t>
+  </si>
+  <si>
+    <t>Ali Pur Chatta</t>
+  </si>
+  <si>
+    <t>Arifwala</t>
+  </si>
+  <si>
+    <t>Attock</t>
+  </si>
+  <si>
+    <t>Badin</t>
+  </si>
+  <si>
+    <t>Bahawalnagar</t>
+  </si>
+  <si>
+    <t>Bahawalpur</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
+    <t>Karachi</t>
+  </si>
+  <si>
     <t>Farrell Ltd</t>
   </si>
   <si>
@@ -47,52 +83,10 @@
     <t>Torp, Stamm and Wilkinson</t>
   </si>
   <si>
-    <t>Abbottabad</t>
-  </si>
-  <si>
-    <t>Abdul Hakim</t>
-  </si>
-  <si>
-    <t>Ahmed Pur East</t>
-  </si>
-  <si>
-    <t>Alipur</t>
-  </si>
-  <si>
-    <t>Ali Pur Chatta</t>
-  </si>
-  <si>
-    <t>Arifwala</t>
-  </si>
-  <si>
-    <t>Attock</t>
-  </si>
-  <si>
-    <t>Badin</t>
-  </si>
-  <si>
-    <t>Bahawalnagar</t>
-  </si>
-  <si>
-    <t>Bahawalpur</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
-  </si>
-  <si>
-    <t>Karachi</t>
-  </si>
-  <si>
     <t>Lahore</t>
   </si>
   <si>
     <t>Multan</t>
-  </si>
-  <si>
-    <t>Rawalpindi</t>
-  </si>
-  <si>
-    <t>Tando Jam</t>
   </si>
 </sst>
 </file>
@@ -431,7 +425,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -446,646 +440,546 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="B6" t="s">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="B7" t="s">
-        <v>6</v>
+      <c r="A7" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="B8" t="s">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>8</v>
+      <c r="A9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" t="s">
-        <v>9</v>
+      <c r="A10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="B12" t="s">
-        <v>4</v>
+      <c r="A12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="B13" t="s">
-        <v>5</v>
+      <c r="A13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="B14" t="s">
-        <v>6</v>
+      <c r="A14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="B15" t="s">
-        <v>7</v>
+      <c r="A15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="B16" t="s">
-        <v>8</v>
+      <c r="A16" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="B17" t="s">
-        <v>9</v>
+      <c r="A17" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="B19" t="s">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="B20" t="s">
-        <v>5</v>
+      <c r="A20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="B21" t="s">
-        <v>6</v>
+      <c r="A21" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="B22" t="s">
-        <v>7</v>
+      <c r="A22" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="B23" t="s">
-        <v>8</v>
+      <c r="A23" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="B24" t="s">
-        <v>9</v>
+      <c r="A24" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="B26" t="s">
-        <v>4</v>
+      <c r="A26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="B27" t="s">
+      <c r="A27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="B28" t="s">
-        <v>6</v>
+      <c r="A28" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="B29" t="s">
-        <v>7</v>
+      <c r="A29" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="B30" t="s">
-        <v>8</v>
+      <c r="A30" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="B31" t="s">
-        <v>9</v>
+      <c r="A31" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="B33" t="s">
-        <v>4</v>
+      <c r="A33" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="B34" t="s">
-        <v>5</v>
+      <c r="A34" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="B35" t="s">
+      <c r="A35" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="B36" t="s">
-        <v>7</v>
+      <c r="A36" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="B37" t="s">
-        <v>8</v>
+      <c r="A37" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="B38" t="s">
-        <v>9</v>
+      <c r="A38" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="B40" t="s">
-        <v>4</v>
+      <c r="A40" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="B41" t="s">
-        <v>5</v>
+      <c r="A41" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="B42" t="s">
-        <v>6</v>
+      <c r="A42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="B43" t="s">
+      <c r="A43" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="B44" t="s">
-        <v>8</v>
+      <c r="A44" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="B45" t="s">
-        <v>9</v>
+      <c r="A45" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="B47" t="s">
-        <v>4</v>
+      <c r="A47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="B48" t="s">
-        <v>5</v>
+      <c r="A48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="B49" t="s">
-        <v>6</v>
+      <c r="A49" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="B50" t="s">
-        <v>7</v>
+      <c r="A50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="B51" t="s">
+      <c r="A51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="B52" t="s">
-        <v>9</v>
+      <c r="A52" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="B54" t="s">
-        <v>4</v>
+      <c r="A54" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="B55" t="s">
-        <v>5</v>
+      <c r="A55" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="B56" t="s">
-        <v>6</v>
+      <c r="A56" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="B57" t="s">
-        <v>7</v>
+      <c r="A57" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="B58" t="s">
-        <v>8</v>
+      <c r="A58" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="B59" t="s">
+      <c r="A59" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>17</v>
-      </c>
-      <c r="B60" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="B61" t="s">
-        <v>4</v>
+      <c r="A61" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="B62" t="s">
-        <v>5</v>
+      <c r="A62" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="B63" t="s">
-        <v>6</v>
+      <c r="A63" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="B64" t="s">
-        <v>7</v>
+      <c r="A64" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="B65" t="s">
-        <v>8</v>
+      <c r="A65" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="B66" t="s">
-        <v>9</v>
+      <c r="A66" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="B68" t="s">
-        <v>4</v>
+      <c r="A68" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="B69" t="s">
-        <v>5</v>
+      <c r="A69" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="B70" t="s">
-        <v>6</v>
+      <c r="A70" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="B71" t="s">
-        <v>7</v>
+      <c r="A71" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="B72" t="s">
-        <v>8</v>
+      <c r="A72" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="B73" t="s">
-        <v>9</v>
+      <c r="A73" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B74" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="B75" t="s">
-        <v>4</v>
+      <c r="A75" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="B76" t="s">
-        <v>5</v>
+      <c r="A76" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="B77" t="s">
-        <v>6</v>
+      <c r="A77" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="B78" t="s">
-        <v>7</v>
+      <c r="A78" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="B79" t="s">
-        <v>8</v>
+      <c r="A79" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="B80" t="s">
-        <v>9</v>
+      <c r="A80" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>20</v>
-      </c>
-      <c r="B81" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="B82" t="s">
-        <v>4</v>
+      <c r="A82" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="B83" t="s">
-        <v>5</v>
+      <c r="A83" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="B84" t="s">
-        <v>6</v>
+      <c r="A84" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="B85" t="s">
-        <v>7</v>
+      <c r="A85" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="B86" t="s">
-        <v>8</v>
+      <c r="A86" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="B87" t="s">
-        <v>9</v>
+      <c r="A87" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
         <v>21</v>
-      </c>
-      <c r="B88" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="B89" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="B90" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="B91" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="B92" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="B94" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>22</v>
       </c>
-      <c r="B95" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="B96" t="s">
-        <v>4</v>
+      <c r="A96" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="B97" t="s">
-        <v>5</v>
+      <c r="A97" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="B98" t="s">
-        <v>6</v>
+      <c r="A98" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="B99" t="s">
-        <v>7</v>
+      <c r="A99" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="B100" t="s">
-        <v>8</v>
+      <c r="A100" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="B101" t="s">
-        <v>9</v>
+      <c r="A101" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>23</v>
       </c>
-      <c r="B102" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="B103" t="s">
-        <v>4</v>
+      <c r="A103" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="B104" t="s">
-        <v>5</v>
+      <c r="A104" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="B105" t="s">
-        <v>6</v>
+      <c r="A105" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="B106" t="s">
-        <v>7</v>
+      <c r="A106" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="B107" t="s">
-        <v>8</v>
+      <c r="A107" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>24</v>
-      </c>
-      <c r="B109" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="B110" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="B111" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="B112" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="B113" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="B114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="B115" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>25</v>
-      </c>
-      <c r="B116" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="B117" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="B118" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="B119" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="B120" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="B121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="B122" t="s">
-        <v>9</v>
+      <c r="A108" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -425,7 +425,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -443,542 +443,104 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>3</v>
+      <c r="B17" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>4</v>
+      <c r="B18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>4</v>
+      <c r="B19" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>4</v>
+      <c r="B20" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>4</v>
+      <c r="B21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>4</v>
+      <c r="B22" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>14</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>14</v>
-      </c>
-      <c r="B91" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
         <v>23</v>
       </c>
     </row>

--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
   <si>
     <t>Origin</t>
   </si>
@@ -23,70 +23,43 @@
     <t>Client Name</t>
   </si>
   <si>
-    <t>Multiple</t>
-  </si>
-  <si>
-    <t>Abbottabad</t>
-  </si>
-  <si>
-    <t>Abdul Hakim</t>
-  </si>
-  <si>
-    <t>Ahmed Pur East</t>
-  </si>
-  <si>
-    <t>Alipur</t>
-  </si>
-  <si>
-    <t>Ali Pur Chatta</t>
-  </si>
-  <si>
-    <t>Arifwala</t>
-  </si>
-  <si>
-    <t>Attock</t>
-  </si>
-  <si>
-    <t>Badin</t>
-  </si>
-  <si>
-    <t>Bahawalnagar</t>
-  </si>
-  <si>
-    <t>Bahawalpur</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
+    <t>February 2018</t>
+  </si>
+  <si>
+    <t>March 2018</t>
+  </si>
+  <si>
+    <t>April 2018</t>
+  </si>
+  <si>
+    <t>May 2018</t>
+  </si>
+  <si>
+    <t>June 2018</t>
+  </si>
+  <si>
+    <t>July 2018</t>
+  </si>
+  <si>
+    <t>August 2018</t>
+  </si>
+  <si>
+    <t>Parcels</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>COD Amount</t>
+  </si>
+  <si>
+    <t>Revenue</t>
   </si>
   <si>
     <t>Karachi</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
-  </si>
-  <si>
-    <t>Murphy PLC</t>
-  </si>
-  <si>
-    <t>Swift LLC</t>
-  </si>
-  <si>
-    <t>Stehr LLC</t>
-  </si>
-  <si>
-    <t>Bruen Inc</t>
-  </si>
-  <si>
-    <t>Mohr-Collier</t>
-  </si>
-  <si>
-    <t>Torp, Stamm and Wilkinson</t>
-  </si>
-  <si>
-    <t>Lahore</t>
-  </si>
-  <si>
-    <t>Multan</t>
   </si>
 </sst>
 </file>
@@ -94,9 +67,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
@@ -122,9 +104,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,127 +410,248 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:30">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>2</v>
+    <row r="2" spans="1:30">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V2" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" t="s">
+        <v>9</v>
+      </c>
+      <c r="X2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+    <row r="4" spans="1:30">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>23</v>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>59</v>
+      </c>
+      <c r="X4">
+        <v>13</v>
+      </c>
+      <c r="Y4">
+        <v>205422</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
+  <mergeCells>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="AA1:AD1"/>
+  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>

--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>Origin</t>
   </si>
@@ -23,12 +23,6 @@
     <t>Client Name</t>
   </si>
   <si>
-    <t>February 2018</t>
-  </si>
-  <si>
-    <t>March 2018</t>
-  </si>
-  <si>
     <t>April 2018</t>
   </si>
   <si>
@@ -56,10 +50,70 @@
     <t>Revenue</t>
   </si>
   <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Abbottabad</t>
+  </si>
+  <si>
+    <t>Abdul Hakim</t>
+  </si>
+  <si>
+    <t>Ahmed Pur East</t>
+  </si>
+  <si>
+    <t>Alipur</t>
+  </si>
+  <si>
+    <t>Ali Pur Chatta</t>
+  </si>
+  <si>
+    <t>Arifwala</t>
+  </si>
+  <si>
+    <t>Attock</t>
+  </si>
+  <si>
+    <t>Badin</t>
+  </si>
+  <si>
+    <t>Bahawalnagar</t>
+  </si>
+  <si>
+    <t>Bahawalpur</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
     <t>Karachi</t>
   </si>
   <si>
     <t>Farrell Ltd</t>
+  </si>
+  <si>
+    <t>Murphy PLC</t>
+  </si>
+  <si>
+    <t>Swift LLC</t>
+  </si>
+  <si>
+    <t>Stehr LLC</t>
+  </si>
+  <si>
+    <t>Bruen Inc</t>
+  </si>
+  <si>
+    <t>Mohr-Collier</t>
+  </si>
+  <si>
+    <t>Torp, Stamm and Wilkinson</t>
+  </si>
+  <si>
+    <t>Lahore</t>
+  </si>
+  <si>
+    <t>Multan</t>
   </si>
 </sst>
 </file>
@@ -410,10 +464,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,195 +504,595 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:22">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>52</v>
+      </c>
+      <c r="P16">
+        <v>13</v>
+      </c>
+      <c r="Q16">
+        <v>183422</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>8</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>2328</v>
+      </c>
+      <c r="R17">
+        <v>50</v>
+      </c>
+      <c r="S17">
+        <v>11</v>
+      </c>
+      <c r="T17">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" t="s">
-        <v>10</v>
-      </c>
-      <c r="U2" t="s">
-        <v>11</v>
-      </c>
-      <c r="V2" t="s">
-        <v>12</v>
-      </c>
-      <c r="W2" t="s">
-        <v>9</v>
-      </c>
-      <c r="X2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>59</v>
-      </c>
-      <c r="X4">
-        <v>13</v>
-      </c>
-      <c r="Y4">
-        <v>205422</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
+      <c r="U17">
+        <v>21542</v>
+      </c>
+      <c r="V17">
+        <v>1763.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>5</v>
+      </c>
+      <c r="P18">
+        <v>5</v>
+      </c>
+      <c r="Q18">
+        <v>15000</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>2</v>
+      </c>
+      <c r="T18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>4222</v>
+      </c>
+      <c r="V18">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1300</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -649,8 +1103,6 @@
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="AA1:AD1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>Origin</t>
   </si>
@@ -23,6 +23,15 @@
     <t>Client Name</t>
   </si>
   <si>
+    <t>April 2018</t>
+  </si>
+  <si>
+    <t>May 2018</t>
+  </si>
+  <si>
+    <t>June 2018</t>
+  </si>
+  <si>
     <t>July 2018</t>
   </si>
   <si>
@@ -44,10 +53,55 @@
     <t>Revenue</t>
   </si>
   <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Abbottabad</t>
+  </si>
+  <si>
+    <t>Bahawalpur</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
     <t>Karachi</t>
   </si>
   <si>
+    <t>Farrell Ltd</t>
+  </si>
+  <si>
+    <t>Murphy PLC</t>
+  </si>
+  <si>
+    <t>Swift LLC</t>
+  </si>
+  <si>
     <t>Stehr LLC</t>
+  </si>
+  <si>
+    <t>Bruen Inc</t>
+  </si>
+  <si>
+    <t>Mohr-Collier</t>
+  </si>
+  <si>
+    <t>Torp, Stamm and Wilkinson</t>
+  </si>
+  <si>
+    <t>Bibi</t>
+  </si>
+  <si>
+    <t>Lahore</t>
+  </si>
+  <si>
+    <t>Multan</t>
+  </si>
+  <si>
+    <t>Another faltu city</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
   </si>
 </sst>
 </file>
@@ -398,10 +452,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,87 +480,756 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26">
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>52</v>
+      </c>
+      <c r="P8">
+        <v>13</v>
+      </c>
+      <c r="Q8">
+        <v>183422</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>2328</v>
+      </c>
+      <c r="R9">
+        <v>50</v>
+      </c>
+      <c r="S9">
+        <v>11</v>
+      </c>
+      <c r="T9">
+        <v>9</v>
+      </c>
+      <c r="U9">
+        <v>21542</v>
+      </c>
+      <c r="V9">
+        <v>1763.8</v>
+      </c>
+      <c r="W9">
+        <v>4</v>
+      </c>
+      <c r="X9">
+        <v>4</v>
+      </c>
+      <c r="Y9">
+        <v>8000</v>
+      </c>
+      <c r="Z9">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="P10">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
+      <c r="Q10">
+        <v>15000</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>2</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>4222</v>
+      </c>
+      <c r="V10">
+        <v>110</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1300</v>
+      </c>
+      <c r="V13">
+        <v>50</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>2000</v>
+      </c>
+      <c r="Z15">
+        <v>235.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -515,6 +1238,9 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:Z1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/reports/customer_sales_report.xlsx
+++ b/public/reports/customer_sales_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
   <si>
     <t>Origin</t>
   </si>
@@ -44,28 +44,7 @@
     <t>Karachi</t>
   </si>
   <si>
-    <t>Farrell Ltd</t>
-  </si>
-  <si>
     <t>Murphy PLC</t>
-  </si>
-  <si>
-    <t>Swift LLC</t>
-  </si>
-  <si>
-    <t>Stehr LLC</t>
-  </si>
-  <si>
-    <t>Bruen Inc</t>
-  </si>
-  <si>
-    <t>Mohr-Collier</t>
-  </si>
-  <si>
-    <t>Torp, Stamm and Wilkinson</t>
-  </si>
-  <si>
-    <t>emarto</t>
   </si>
 </sst>
 </file>
@@ -416,7 +395,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -460,135 +439,16 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>11075</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>11075</v>
-      </c>
-      <c r="F6">
         <v>1480.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>11305</v>
-      </c>
-      <c r="F10">
-        <v>1158.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
-      </c>
-      <c r="E12">
-        <v>15000</v>
-      </c>
-      <c r="F12">
-        <v>1521</v>
       </c>
     </row>
   </sheetData>
